--- a/Outputs/Scenarios/PtX_demand_HU_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_HU_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.002344042396197738</v>
       </c>
       <c r="K16" t="n">
-        <v>7.389742501572564e-05</v>
+        <v>0.0001724273250366932</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0001231623750262094</v>
+        <v>5.172819751100797e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1370,7 +1370,7 @@
         <v>0.001137068519571234</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0009684853274797893</v>
+        <v>0.0009684853274797894</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>3.377368313089167e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>4.926495001048377e-05</v>
+        <v>2.21692275047177e-05</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.00347006938884947</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0003699816232180017</v>
+        <v>0.0008632904541753374</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0006166360386966695</v>
+        <v>0.0002589871362526012</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>0.0001826352309920774</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0002466544154786678</v>
+        <v>0.0001109944869654005</v>
       </c>
     </row>
     <row r="43">
